--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$266</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
   </definedNames>
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G268" headerRowCount="1">
-  <autoFilter ref="A1:G268"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G266" headerRowCount="1">
+  <autoFilter ref="A1:G266"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -12409,7 +12409,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="51" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
@@ -13055,70 +13055,78 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>isPrimary</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SPI_DATA.csv:Main alternative par equals material/part number</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Populated from SPI_DATA.csv Main alternative par. Blank when SPI has no main alternative value.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>primaryPartNumber</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>SPI_DATA.csv:Main alternative par</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Populated from SPI_DATA.csv Main alternative par. Blank when SPI has no main alternative value.</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13202,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13240,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13274,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13308,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13342,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13376,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13410,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13444,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13478,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13512,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13546,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13580,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13618,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13656,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -23231,7 +23239,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>isPrimary</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -23251,7 +23259,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isPrimary?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -23261,14 +23269,14 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>primaryPartNumber</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -23288,7 +23296,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.primaryPartNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -23298,14 +23306,14 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>productClass</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -23325,7 +23333,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -23335,14 +23343,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -23362,7 +23370,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -23372,14 +23380,14 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>productClass</t>
+          <t>costCategory</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -23399,7 +23407,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -23409,14 +23417,14 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -23436,7 +23444,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -23446,14 +23454,14 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>costCategory</t>
+          <t>isKit</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -23473,7 +23481,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -23483,14 +23491,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>isObsolete</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -23510,7 +23518,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isObsolete?</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -23520,14 +23528,14 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>isKit</t>
+          <t>isService</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -23547,7 +23555,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isService?</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -23557,14 +23565,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>isObsolete</t>
+          <t>isTool</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -23584,7 +23592,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isObsolete?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isTool?</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -23594,14 +23602,14 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>isService</t>
+          <t>isExcludeFromReplenishment</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -23621,7 +23629,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isService?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -23631,14 +23639,14 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>isTool</t>
+          <t>isSmallPart</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -23658,7 +23666,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isTool?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isSmallPart?</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -23668,14 +23676,14 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>isExcludeFromReplenishment</t>
+          <t>purchaseLeadTimeDays</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -23695,7 +23703,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -23705,14 +23713,14 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>isSmallPart</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -23732,7 +23740,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isSmallPart?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -23742,19 +23750,19 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>purchaseLeadTimeDays</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -23769,7 +23777,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -23786,12 +23794,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -23806,7 +23814,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -23823,7 +23831,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>addressLine1</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -23843,7 +23851,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -23860,7 +23868,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -23880,7 +23888,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -23897,7 +23905,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>addressLine1</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -23917,7 +23925,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -23934,7 +23942,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -23954,7 +23962,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -23971,7 +23979,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -23991,7 +23999,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -24008,7 +24016,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -24028,7 +24036,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -24045,7 +24053,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -24065,7 +24073,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -24082,7 +24090,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -24102,7 +24110,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -24119,7 +24127,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -24139,7 +24147,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -24156,7 +24164,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -24176,7 +24184,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -24193,12 +24201,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -24213,7 +24221,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -24235,7 +24243,7 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -24250,7 +24258,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.nodeId?</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -24267,7 +24275,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>returnWarehouseId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -24287,7 +24295,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -24304,7 +24312,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>supplyWarehouseId</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -24324,7 +24332,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -24341,7 +24349,7 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>returnWarehouseId</t>
+          <t>warehouseTypeId</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -24361,7 +24369,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -24378,7 +24386,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>supplyWarehouseId</t>
+          <t>isRepairWarehouse</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -24398,7 +24406,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRepairWarehouse?</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -24415,7 +24423,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>warehouseTypeId</t>
+          <t>isReplenishable</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -24435,7 +24443,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -24452,7 +24460,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>isRepairWarehouse</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -24472,7 +24480,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRepairWarehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBootStockable?</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -24489,7 +24497,7 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>isReplenishable</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -24509,7 +24517,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -24526,7 +24534,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>isRemote</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -24546,7 +24554,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -24563,7 +24571,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>warehouseStatusId</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -24583,7 +24591,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -24600,12 +24608,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>isRemote</t>
+          <t>inventoryType</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -24620,7 +24628,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -24637,12 +24645,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>warehouseStatusId</t>
+          <t>quantityOutbound</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -24657,7 +24665,7 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -24674,12 +24682,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>inventoryType</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -24694,7 +24702,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -24711,12 +24719,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>quantityOutbound</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -24731,7 +24739,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -24748,7 +24756,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>actionGroupId</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -24768,7 +24776,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.actionGroupId?</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -24785,7 +24793,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -24805,7 +24813,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -24822,7 +24830,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -24842,7 +24850,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -24859,7 +24867,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -24879,7 +24887,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -24896,7 +24904,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -24916,7 +24924,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -24933,7 +24941,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -24953,7 +24961,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -24970,7 +24978,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -24990,7 +24998,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -25007,7 +25015,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -25027,7 +25035,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -25044,12 +25052,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -25064,7 +25072,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderNumber?</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -25081,12 +25089,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -25101,7 +25109,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -25118,7 +25126,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -25138,7 +25146,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -25155,7 +25163,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -25175,7 +25183,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -25192,7 +25200,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -25212,7 +25220,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -25229,7 +25237,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -25249,7 +25257,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -25266,7 +25274,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -25286,7 +25294,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -25303,7 +25311,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -25323,7 +25331,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -25340,7 +25348,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -25360,7 +25368,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partCode?</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -25377,7 +25385,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -25397,7 +25405,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.Warehouse?</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -25414,7 +25422,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -25434,7 +25442,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -25451,7 +25459,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -25471,7 +25479,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -25488,7 +25496,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -25508,7 +25516,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -25525,7 +25533,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -25545,7 +25553,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.quantityUsed?</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -25562,7 +25570,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -25582,7 +25590,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -25599,7 +25607,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -25619,7 +25627,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -25636,7 +25644,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -25656,7 +25664,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -25673,12 +25681,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -25693,7 +25701,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -25710,12 +25718,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -25730,7 +25738,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -25747,7 +25755,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -25767,7 +25775,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -25784,7 +25792,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -25804,7 +25812,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -25821,7 +25829,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -25841,7 +25849,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -25858,7 +25866,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -25878,7 +25886,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -25895,7 +25903,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -25915,7 +25923,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -25932,7 +25940,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -25952,7 +25960,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -25969,7 +25977,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -25989,7 +25997,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -26006,7 +26014,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -26026,7 +26034,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -26043,7 +26051,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -26063,7 +26071,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -26080,7 +26088,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -26100,7 +26108,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -26117,12 +26125,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -26137,7 +26145,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -26154,12 +26162,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -26174,7 +26182,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -26191,7 +26199,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -26211,7 +26219,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -26228,7 +26236,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -26248,7 +26256,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -26265,7 +26273,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -26285,7 +26293,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -26302,7 +26310,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -26322,7 +26330,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -26339,7 +26347,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -26359,7 +26367,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -26376,7 +26384,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -26396,7 +26404,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -26413,7 +26421,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -26433,7 +26441,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -26450,7 +26458,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -26470,7 +26478,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -26487,7 +26495,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -26507,7 +26515,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -26524,7 +26532,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -26544,7 +26552,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -26561,7 +26569,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -26581,7 +26589,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -26598,7 +26606,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -26618,7 +26626,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -26635,7 +26643,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -26655,7 +26663,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -26672,7 +26680,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -26692,7 +26700,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -26709,7 +26717,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -26729,7 +26737,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -26746,7 +26754,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -26766,7 +26774,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -26783,7 +26791,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -26803,7 +26811,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -26820,7 +26828,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -26840,7 +26848,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -26857,7 +26865,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -26877,7 +26885,7 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -26894,7 +26902,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -26914,7 +26922,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -26931,12 +26939,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -26951,7 +26959,7 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -26968,12 +26976,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -26988,7 +26996,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -27005,7 +27013,7 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -27025,7 +27033,7 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -27042,7 +27050,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -27062,7 +27070,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -27079,7 +27087,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>averageRepairCost</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -27099,7 +27107,7 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -27116,12 +27124,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -27136,7 +27144,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -27153,12 +27161,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>averageRepairCost</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -27173,7 +27181,7 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -27190,7 +27198,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -27210,7 +27218,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -27227,12 +27235,12 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
@@ -27247,7 +27255,7 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -27264,12 +27272,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -27284,7 +27292,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -27301,7 +27309,7 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -27321,7 +27329,7 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
@@ -27338,7 +27346,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -27358,7 +27366,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -27375,7 +27383,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -27395,7 +27403,7 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -27412,7 +27420,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -27432,7 +27440,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -27449,7 +27457,7 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -27469,7 +27477,7 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -27486,7 +27494,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>loClass</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -27506,7 +27514,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -27523,7 +27531,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -27543,7 +27551,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -27560,7 +27568,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>loClass</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -27580,7 +27588,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -27597,7 +27605,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -27617,7 +27625,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -27634,7 +27642,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -27654,7 +27662,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -27671,7 +27679,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -27691,7 +27699,7 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -27708,7 +27716,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -27728,7 +27736,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -27745,12 +27753,12 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>purchaseOrderNumber</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -27765,7 +27773,7 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -27782,12 +27790,12 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>purchaseOrderStatus</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -27802,7 +27810,7 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -27819,7 +27827,7 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>creationDateTime</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -27839,7 +27847,7 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -27856,7 +27864,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>approvalDateTime</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -27876,7 +27884,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -27893,7 +27901,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -27913,7 +27921,7 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -27930,7 +27938,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>approvalDateTime</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -27950,7 +27958,7 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -27967,7 +27975,7 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -27987,7 +27995,7 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -28004,7 +28012,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -28024,7 +28032,7 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -28041,7 +28049,7 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -28061,7 +28069,7 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -28078,7 +28086,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -28098,7 +28106,7 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -28115,7 +28123,7 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -28135,7 +28143,7 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -28152,7 +28160,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -28172,7 +28180,7 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -28189,7 +28197,7 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>lineCost</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -28209,7 +28217,7 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -28226,7 +28234,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>quantityReceived</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -28246,7 +28254,7 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -28263,7 +28271,7 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>lineCost</t>
+          <t>receivedDateTime</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -28283,7 +28291,7 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -28300,12 +28308,12 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>quantityReceived</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -28320,7 +28328,7 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -28337,12 +28345,12 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>receivedDateTime</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -28357,7 +28365,7 @@
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -28374,12 +28382,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -28394,7 +28402,7 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -28411,12 +28419,12 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -28431,7 +28439,7 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
@@ -28448,7 +28456,7 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -28468,7 +28476,7 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -28485,12 +28493,12 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>actionGroupId</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -28505,7 +28513,7 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -28522,12 +28530,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -28542,7 +28550,7 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -28559,7 +28567,7 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>actionGroupDescription</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -28579,7 +28587,7 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -28596,7 +28604,7 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -28616,7 +28624,7 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -28633,7 +28641,7 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>actionGroupDescription</t>
+          <t>isUsed</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -28653,7 +28661,7 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -28670,7 +28678,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>isObsolete</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -28690,7 +28698,7 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -28707,12 +28715,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>isUsed</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -28727,7 +28735,7 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -28744,12 +28752,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>isObsolete</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -28764,7 +28772,7 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -28781,7 +28789,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>warehouseId</t>
+          <t>exclusion</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -28801,7 +28809,7 @@
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
@@ -28815,82 +28823,8 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D267" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E267" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="F267" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G267" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D268" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="F268" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G268" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G268"/>
+  <autoFilter ref="A1:G266"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -29391,7 +29325,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>isPrimary; primaryPartNumber; isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
+          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$266</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -218,8 +218,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D12" headerRowCount="1">
-  <autoFilter ref="A1:D12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D13" headerRowCount="1">
+  <autoFilter ref="A1:D13"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Source"/>
     <tableColumn id="2" name="Path"/>
@@ -12408,7 +12408,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
@@ -13263,7 +13263,7 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -13274,7 +13274,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13365,7 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18954,8 +18954,30 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Live SAP item group check</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>MinStock3 SAP Service Layer credentials</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Checked Items and ItemGroups while VPN was connected. ItemGroups are broad customer/manufacturer groups such as FUJITSU, ACER, and CHOICE; sampled item master fields ItemType, ItemClass, and MaterialType are generic SAP classifications.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -18975,7 +18997,7 @@
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
@@ -23328,7 +23350,7 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -23343,7 +23365,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -23365,7 +23387,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -23380,7 +23402,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
@@ -23439,7 +23461,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -23454,7 +23476,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Left blank. CoCre8 local reporting has only item group codes; live SAP ItemGroups/OITM needs investigation for class/type semantics.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Target Fields" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Template Fields" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Source Evidence" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Unknowns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Output Objects" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SAP Investigation Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Fields" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Fields" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Evidence" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unknowns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output Objects" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP Investigation Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$153</definedName>
@@ -12623,7 +12623,7 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12695,7 @@
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12763,7 @@
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard response time.</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
         </is>
       </c>
     </row>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
@@ -22943,7 +22943,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
         </is>
       </c>
     </row>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -23032,7 +23032,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
         </is>
       </c>
     </row>
@@ -23054,7 +23054,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -23069,7 +23069,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
         </is>
       </c>
     </row>
@@ -23091,7 +23091,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard response time.</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
         </is>
       </c>
     </row>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
         </is>
       </c>
     </row>
@@ -24290,7 +24290,7 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
         </is>
       </c>
     </row>
@@ -24327,7 +24327,7 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
         </is>
       </c>
     </row>
@@ -24401,7 +24401,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
         </is>
       </c>
     </row>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
         </is>
       </c>
     </row>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24512,7 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
         </is>
       </c>
     </row>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
         </is>
       </c>
     </row>
@@ -24586,7 +24586,7 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
         </is>
       </c>
     </row>
@@ -24623,7 +24623,7 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$270</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
   </definedNames>
@@ -218,8 +218,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D13" headerRowCount="1">
-  <autoFilter ref="A1:D13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D12" headerRowCount="1">
+  <autoFilter ref="A1:D12"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Source"/>
     <tableColumn id="2" name="Path"/>
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G266" headerRowCount="1">
-  <autoFilter ref="A1:G266"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G270" headerRowCount="1">
+  <autoFilter ref="A1:G270"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       <c r="O81" s="2" t="inlineStr"/>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7436,12 +7436,12 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Stock audit / Exco Usage</t>
+          <t>Manual SAP stock audit report</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report / Usage.csv</t>
+          <t>Stock Audit Report</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Usage is confirmed at item/warehouse/date grain; work-order linkage may need SAP verification.</t>
+          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
         </is>
       </c>
     </row>
@@ -10798,12 +10798,12 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -11612,12 +11612,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Local dimension</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>warehouse_dimension.csv / FactWarehouses.csv</t>
+          <t>Warehouses endpoint</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -12056,12 +12056,12 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -12130,12 +12130,12 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -12204,12 +12204,12 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -12278,12 +12278,12 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -12352,12 +12352,12 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>SAP + Exco</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>OITW / InventoryCurrent.csv</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
@@ -12567,40 +12567,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Customers</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>customerId</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Exco Customers.csv:CustomerCode</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Investigate source</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
@@ -12639,40 +12635,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Customers</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Exco Customers.csv:CustomerName</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Investigate source</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
@@ -12979,40 +12971,36 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>SPLMaster</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Exco Parts.csv:SPLMaster</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13028,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Exco Parts.csv:ItemNo</t>
+          <t>SAP Service Layer SQLQueries:OITM.ItemCode</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13050,7 +13038,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13142,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Exco Parts.csv:ItemDescription/DisplayDescription</t>
+          <t>SAP Service Layer SQLQueries:OITM.ItemName</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13164,7 +13152,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14084,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Exco Warehouses.csv:WarehouseCode</t>
+          <t>SAP Service Layer Warehouses:WarehouseCode</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14106,7 +14094,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14121,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -14171,7 +14159,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -14209,7 +14197,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
@@ -14247,7 +14235,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -14285,7 +14273,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -14324,7 +14312,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Exco Warehouses.csv:WarehouseName</t>
+          <t>SAP Service Layer Warehouses:WarehouseName</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -14334,7 +14322,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14345,7 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
@@ -14391,7 +14379,7 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -14425,7 +14413,7 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -14459,7 +14447,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -14493,7 +14481,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -14531,7 +14519,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -14570,7 +14558,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Exco InventoryCurrent.csv:ItemNo</t>
+          <t>SAP Service Layer SQLQueries:OITW.ItemCode</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14580,7 +14568,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14596,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Exco InventoryCurrent.csv:WarehouseCode</t>
+          <t>SAP Service Layer SQLQueries:OITW.WhsCode</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -14618,7 +14606,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14629,7 @@
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -14652,7 +14640,7 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14668,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Exco InventoryCurrent.csv:Commited</t>
+          <t>SAP Service Layer SQLQueries:OITW.IsCommited</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14690,7 +14678,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14706,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Exco InventoryCurrent.csv:Quantity</t>
+          <t>SAP Service Layer SQLQueries:OITW.OnHand</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -14728,7 +14716,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14744,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Exco InventoryCurrent.csv:Ordered</t>
+          <t>SAP Service Layer SQLQueries:OITW.OnOrder</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -14766,7 +14754,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14777,7 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -14800,45 +14788,41 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>uniqueId</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Derived stable key partCode|warehouseCode</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed local CoCre8/Exco source.</t>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Investigate source</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
         </is>
       </c>
     </row>
@@ -18681,11 +18665,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
@@ -18781,22 +18765,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>MinStock3 warehouse/customer</t>
+          <t>SAP live warehouse lookup</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\MinStock3\enrich_dimensions.py</t>
+          <t>Service Layer Warehouses endpoint</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>FactWarehouses.csv and customers.csv enrich warehouse/customer dimensions.</t>
+          <t>WarehouseCode and WarehouseName are fetched live for warehouses present in live stock rows.</t>
         </is>
       </c>
     </row>
@@ -18847,34 +18831,34 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Exco inventory output</t>
+          <t>Planning V2 live stock extract</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\Exco\output\csv\InventoryCurrent.csv</t>
+          <t>Service Layer SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Current stock, warehouse/customer, item, price, bin, and cost fields.</t>
+          <t>Current stock metrics are fetched live from OITW: OnHand, IsCommited, OnOrder, MinStock, MaxStock, AvgPrice.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Exco usage output</t>
+          <t>Manual stock audit report</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\Exco\output\csv\Usage.csv</t>
+          <t>C:\dev\cc8\Exco\source_data\Stock Audit Report.txt</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -18884,19 +18868,19 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Usage fact by posting date, item, warehouse, customer, and quantity.</t>
+          <t>Allowed manual SAP report source for usage once mapped to the template.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Exco stock flow output</t>
+          <t>Reference target fields</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\Exco\output\csv\StockFlow.csv</t>
+          <t>Reference\SPL Planning Data Fields.xlsx</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -18906,19 +18890,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>All stock audit movements by document type and signed quantity.</t>
+          <t>Planning V2 target field metadata and CC8 relevance hints.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Reference target fields</t>
+          <t>Planning V2 sample templates</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Reference\SPL Planning Data Fields.xlsx</t>
+          <t>Samples\Templates raw.xlsx</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -18928,56 +18912,34 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Planning V2 target field metadata and CC8 relevance hints.</t>
+          <t>Canonical onboarding template fields used for template-shaped CSV outputs.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Planning V2 sample templates</t>
+          <t>Live SAP item group check</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Samples\Templates raw.xlsx</t>
+          <t>MinStock3 SAP Service Layer credentials</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Canonical onboarding template fields used for template-shaped CSV outputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Live SAP item group check</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MinStock3 SAP Service Layer credentials</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
           <t>Checked Items and ItemGroups while VPN was connected. ItemGroups are broad customer/manufacturer groups such as FUJITSU, ACER, and CHOICE; sampled item master fields ItemType, ItemClass, and MaterialType are generic SAP classifications.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D13"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -18991,7 +18953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -22891,7 +22853,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>customerGroupId</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -22911,7 +22873,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerId?</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -22921,14 +22883,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
+          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>customerGroupId</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -22948,7 +22910,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -22958,14 +22920,14 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -22985,7 +22947,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.Description?</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -22995,14 +22957,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
+          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>dseSlaCost</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -23022,7 +22984,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -23032,14 +22994,14 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
+          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>dseSlaRevenue</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -23059,7 +23021,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -23069,14 +23031,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
+          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>stdResponseTime</t>
+          <t>dseSlaCost</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -23096,7 +23058,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -23106,14 +23068,14 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard response time.</t>
+          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>stdRepairTime</t>
+          <t>dseSlaRevenue</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -23133,7 +23095,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -23143,19 +23105,19 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
+          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>stdResponseTime</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -23165,12 +23127,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -23180,19 +23142,19 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard response time.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>stdRepairTime</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -23202,12 +23164,12 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.Description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -23217,14 +23179,14 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -23244,7 +23206,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorId?</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -23261,12 +23223,12 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Vendors</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -23281,7 +23243,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.Description?</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -23291,19 +23253,19 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Vendors</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -23318,7 +23280,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.isActive?</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -23328,14 +23290,14 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>productClass</t>
+          <t>SPLMaster</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -23350,12 +23312,12 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.SPLMaster?</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -23365,14 +23327,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -23387,12 +23349,12 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -23402,14 +23364,14 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>costCategory</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -23429,7 +23391,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -23446,7 +23408,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>productClass</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -23466,7 +23428,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -23483,7 +23445,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>isKit</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -23498,12 +23460,12 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -23513,14 +23475,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>isObsolete</t>
+          <t>costCategory</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -23540,7 +23502,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isObsolete?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -23557,7 +23519,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>isService</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -23572,12 +23534,12 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isService?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -23587,14 +23549,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>isTool</t>
+          <t>isKit</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -23614,7 +23576,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isTool?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -23631,7 +23593,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>isExcludeFromReplenishment</t>
+          <t>isObsolete</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -23651,7 +23613,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isObsolete?</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -23668,7 +23630,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>isSmallPart</t>
+          <t>isService</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -23688,7 +23650,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isSmallPart?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isService?</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -23705,7 +23667,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>purchaseLeadTimeDays</t>
+          <t>isTool</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -23725,7 +23687,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isTool?</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -23742,7 +23704,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>isExcludeFromReplenishment</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -23762,7 +23724,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -23779,12 +23741,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>isSmallPart</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -23799,7 +23761,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isSmallPart?</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -23809,19 +23771,19 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>purchaseLeadTimeDays</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -23836,7 +23798,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -23846,19 +23808,19 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>addressLine1</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -23873,7 +23835,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -23883,14 +23845,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -23910,7 +23872,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -23927,7 +23889,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -23947,7 +23909,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -23964,7 +23926,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>addressLine1</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -23984,7 +23946,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -24001,7 +23963,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -24021,7 +23983,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -24038,7 +24000,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -24058,7 +24020,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -24075,7 +24037,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -24095,7 +24057,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -24112,7 +24074,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -24132,7 +24094,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -24149,7 +24111,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -24169,7 +24131,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -24186,7 +24148,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -24206,7 +24168,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -24223,12 +24185,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -24243,7 +24205,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -24253,19 +24215,19 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -24280,7 +24242,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -24290,19 +24252,19 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>returnWarehouseId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -24317,7 +24279,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -24327,14 +24289,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>supplyWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -24349,12 +24311,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -24364,14 +24326,14 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
+          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>warehouseTypeId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -24386,12 +24348,12 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.nodeId?</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -24401,14 +24363,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
+          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>isRepairWarehouse</t>
+          <t>returnWarehouseId</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -24423,12 +24385,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRepairWarehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -24438,14 +24400,14 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
+          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>isReplenishable</t>
+          <t>supplyWarehouseId</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -24460,12 +24422,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -24475,14 +24437,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
+          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>warehouseTypeId</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -24497,12 +24459,12 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -24512,14 +24474,14 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
+          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>isRepairWarehouse</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -24534,12 +24496,12 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRepairWarehouse?</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -24549,14 +24511,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
+          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>isRemote</t>
+          <t>isReplenishable</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -24571,12 +24533,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -24586,14 +24548,14 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
+          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>warehouseStatusId</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -24608,12 +24570,12 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBootStockable?</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -24623,19 +24585,19 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
+          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>inventoryType</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -24645,12 +24607,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -24660,19 +24622,19 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>quantityOutbound</t>
+          <t>isRemote</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -24682,12 +24644,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -24697,19 +24659,19 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>warehouseStatusId</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -24719,12 +24681,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -24734,19 +24696,19 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>inventoryType</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -24756,12 +24718,12 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -24771,19 +24733,19 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>quantityOutbound</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -24793,12 +24755,12 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -24808,19 +24770,19 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>uniqueId</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -24830,12 +24792,12 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.uniqueId?</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -24845,14 +24807,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -24872,7 +24834,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -24889,7 +24851,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -24909,7 +24871,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -24926,7 +24888,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>actionGroupId</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -24946,7 +24908,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.actionGroupId?</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -24963,7 +24925,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -24983,7 +24945,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -25000,7 +24962,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -25020,7 +24982,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -25037,7 +24999,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -25057,7 +25019,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -25074,12 +25036,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -25094,7 +25056,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -25111,12 +25073,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -25131,7 +25093,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -25148,12 +25110,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -25168,7 +25130,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -25185,12 +25147,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -25205,7 +25167,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -25222,7 +25184,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -25242,7 +25204,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderNumber?</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -25259,7 +25221,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -25279,7 +25241,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -25296,7 +25258,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -25316,7 +25278,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -25333,7 +25295,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -25353,7 +25315,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -25370,7 +25332,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -25390,7 +25352,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -25407,7 +25369,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -25427,7 +25389,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -25444,7 +25406,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -25464,7 +25426,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -25481,7 +25443,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -25501,7 +25463,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -25518,7 +25480,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -25538,7 +25500,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partCode?</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -25555,7 +25517,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -25575,7 +25537,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.Warehouse?</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -25592,7 +25554,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -25612,7 +25574,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -25629,7 +25591,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -25649,7 +25611,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -25666,7 +25628,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -25686,7 +25648,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -25703,12 +25665,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -25723,7 +25685,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.quantityUsed?</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -25740,12 +25702,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -25760,7 +25722,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -25777,12 +25739,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -25797,7 +25759,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -25814,12 +25776,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -25834,7 +25796,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -25851,7 +25813,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -25871,7 +25833,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -25888,7 +25850,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -25908,7 +25870,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -25925,7 +25887,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -25945,7 +25907,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -25962,7 +25924,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -25982,7 +25944,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -25999,7 +25961,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -26019,7 +25981,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -26036,7 +25998,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -26056,7 +26018,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -26073,7 +26035,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -26093,7 +26055,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -26110,7 +26072,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -26130,7 +26092,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -26147,12 +26109,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -26167,7 +26129,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -26184,12 +26146,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -26204,7 +26166,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -26221,12 +26183,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -26241,7 +26203,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -26258,12 +26220,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -26278,7 +26240,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -26295,7 +26257,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -26315,7 +26277,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -26332,7 +26294,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -26352,7 +26314,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -26369,7 +26331,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -26389,7 +26351,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -26406,7 +26368,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -26426,7 +26388,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -26443,7 +26405,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -26463,7 +26425,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -26480,7 +26442,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -26500,7 +26462,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -26517,7 +26479,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -26537,7 +26499,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -26554,7 +26516,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -26574,7 +26536,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -26591,7 +26553,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -26611,7 +26573,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -26628,7 +26590,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -26648,7 +26610,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -26665,7 +26627,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -26685,7 +26647,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -26702,7 +26664,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -26722,7 +26684,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -26739,7 +26701,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -26759,7 +26721,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -26776,7 +26738,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -26796,7 +26758,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -26813,7 +26775,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -26833,7 +26795,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -26850,7 +26812,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -26870,7 +26832,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -26887,7 +26849,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -26907,7 +26869,7 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -26924,7 +26886,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -26944,7 +26906,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -26961,12 +26923,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -26981,7 +26943,7 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -26998,12 +26960,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -27018,7 +26980,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -27035,12 +26997,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -27055,7 +27017,7 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -27072,12 +27034,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -27092,7 +27054,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -27109,7 +27071,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>averageRepairCost</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -27129,7 +27091,7 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -27146,12 +27108,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -27166,7 +27128,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -27183,12 +27145,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -27203,7 +27165,7 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -27220,12 +27182,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -27240,7 +27202,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -27257,12 +27219,12 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>averageRepairCost</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
@@ -27277,7 +27239,7 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -27294,12 +27256,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -27314,7 +27276,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -27331,12 +27293,12 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -27351,7 +27313,7 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
@@ -27368,12 +27330,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -27388,7 +27350,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -27405,7 +27367,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -27425,7 +27387,7 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -27442,7 +27404,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -27462,7 +27424,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -27479,7 +27441,7 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -27499,7 +27461,7 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -27516,7 +27478,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>loClass</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -27536,7 +27498,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -27553,7 +27515,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -27573,7 +27535,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -27590,7 +27552,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -27610,7 +27572,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -27627,7 +27589,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -27647,7 +27609,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -27664,7 +27626,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>loClass</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -27684,7 +27646,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -27701,7 +27663,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -27721,7 +27683,7 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -27738,7 +27700,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -27758,7 +27720,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -27775,12 +27737,12 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -27795,7 +27757,7 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -27812,12 +27774,12 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -27832,7 +27794,7 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -27849,12 +27811,12 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -27869,7 +27831,7 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -27886,12 +27848,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>approvalDateTime</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -27906,7 +27868,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -27923,7 +27885,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>purchaseOrderNumber</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -27943,7 +27905,7 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -27960,7 +27922,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>purchaseOrderStatus</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -27980,7 +27942,7 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -27997,7 +27959,7 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>creationDateTime</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -28017,7 +27979,7 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -28034,7 +27996,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>approvalDateTime</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -28054,7 +28016,7 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -28071,7 +28033,7 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -28091,7 +28053,7 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -28108,7 +28070,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -28128,7 +28090,7 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -28145,7 +28107,7 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -28165,7 +28127,7 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -28182,7 +28144,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -28202,7 +28164,7 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -28219,7 +28181,7 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>lineCost</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -28239,7 +28201,7 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -28256,7 +28218,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>quantityReceived</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -28276,7 +28238,7 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -28293,7 +28255,7 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>receivedDateTime</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -28313,7 +28275,7 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -28330,12 +28292,12 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -28350,7 +28312,7 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -28367,12 +28329,12 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>lineCost</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -28387,7 +28349,7 @@
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -28404,12 +28366,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>quantityReceived</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -28424,7 +28386,7 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -28441,12 +28403,12 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>receivedDateTime</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -28461,7 +28423,7 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
@@ -28478,12 +28440,12 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -28498,7 +28460,7 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -28515,12 +28477,12 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -28535,7 +28497,7 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -28552,12 +28514,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -28572,7 +28534,7 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -28589,12 +28551,12 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>actionGroupDescription</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -28609,7 +28571,7 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -28626,12 +28588,12 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -28646,7 +28608,7 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -28663,7 +28625,7 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>isUsed</t>
+          <t>actionGroupId</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -28683,7 +28645,7 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -28700,7 +28662,7 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>isObsolete</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -28720,7 +28682,7 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -28737,12 +28699,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>warehouseId</t>
+          <t>actionGroupDescription</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -28757,7 +28719,7 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -28774,12 +28736,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>exclusionType</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -28794,7 +28756,7 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -28811,42 +28773,190 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
+          <t>isUsed</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>isObsolete</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
+        </is>
+      </c>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>warehouseId</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
+        </is>
+      </c>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>exclusionType</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
+        </is>
+      </c>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
           <t>exclusion</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
+      <c r="B270" s="4" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="C266" s="4" t="inlineStr">
+      <c r="C270" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D266" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E266" s="4" t="inlineStr">
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
         <is>
           <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
-      <c r="F266" s="4" t="inlineStr">
+      <c r="F270" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="G266" s="4" t="inlineStr">
+      <c r="G270" s="4" t="inlineStr">
         <is>
           <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G266"/>
+  <autoFilter ref="A1:G270"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -29271,29 +29381,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Customers</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Customers.csv</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Pending/header only</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>customerId, customerGroupId, Description, assignAnySkill, isActive, dseSlaCost, dseSlaRevenue, stdResponseTime, stdRepairTime</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>customerGroupId; assignAnySkill; isActive; dseSlaCost; dseSlaRevenue; stdResponseTime; stdRepairTime</t>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>customerId; customerGroupId; Description; assignAnySkill; isActive; dseSlaCost; dseSlaRevenue; stdResponseTime; stdRepairTime</t>
         </is>
       </c>
     </row>
@@ -29347,7 +29457,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
+          <t>SPLMaster; isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
         </is>
       </c>
     </row>
@@ -29428,7 +29538,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>inventoryType; quantityOutbound</t>
+          <t>inventoryType; quantityOutbound; uniqueId</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP Investigation Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$265</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
   </definedNames>
@@ -176,8 +176,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TargetFields" displayName="TargetFields" ref="A1:P153" headerRowCount="1">
-  <autoFilter ref="A1:P153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TargetFields" displayName="TargetFields" ref="A1:P151" headerRowCount="1">
+  <autoFilter ref="A1:P151"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Reference Row"/>
     <tableColumn id="2" name="Field"/>
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G270" headerRowCount="1">
-  <autoFilter ref="A1:G270"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G265" headerRowCount="1">
+  <autoFilter ref="A1:G265"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7981,7 +7981,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8055,7 +8059,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8129,7 +8137,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8203,7 +8215,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8277,7 +8293,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8351,7 +8371,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8425,7 +8449,11 @@
           <t>Maybe</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>SAP contacts info</t>
+        </is>
+      </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8494,8 +8522,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8568,8 +8604,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8642,8 +8686,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8716,8 +8768,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8790,8 +8850,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8864,8 +8932,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -8938,8 +9014,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9012,8 +9096,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
@@ -9086,8 +9178,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9160,8 +9260,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
           <t>Float</t>
@@ -9234,8 +9342,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
           <t>Float</t>
@@ -9308,8 +9424,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
@@ -9378,8 +9502,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>SAP PO's</t>
+        </is>
+      </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9429,31 +9561,39 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>actual_eta_datetime</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9471,12 +9611,12 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>actual_eta_datetime</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -9491,7 +9631,7 @@
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>Repair order id</t>
+          <t>Datetime when the technician was expect to complete</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
@@ -9503,31 +9643,39 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>repair_type</t>
+          <t>actual_recall_datetime</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9545,12 +9693,12 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>repair_type</t>
+          <t>actual_recall_datetime</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -9565,7 +9713,7 @@
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>Internal or external repair</t>
+          <t>Datetime when call management (FE assignment) was complete</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
@@ -9577,31 +9725,39 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>order_type_id</t>
+          <t>actual_resolve_date</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9619,12 +9775,12 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>order_type_id</t>
+          <t>actual_resolve_date</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -9639,7 +9795,7 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>Rework, repair, etc</t>
+          <t>Datetime when call was closed</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -9651,31 +9807,39 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>creation_datetime</t>
+          <t>actual_resolve_time</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9693,12 +9857,12 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>creation_datetime</t>
+          <t>actual_resolve_time</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -9713,7 +9877,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Datetime when call was closed</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
@@ -9725,31 +9889,39 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>170</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Order_Open_dateTime</t>
+          <t>eta_date</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9767,12 +9939,12 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>Order_Open_dateTime</t>
+          <t>eta_date</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -9787,7 +9959,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>Parts order time</t>
+          <t>Expected ETA</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
@@ -9799,31 +9971,39 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>171</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Item_received_dateTime</t>
+          <t>eta_time</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9841,12 +10021,12 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>Item_received_dateTime</t>
+          <t>eta_time</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -9861,7 +10041,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>Parts receipt time</t>
+          <t>Expected ETA</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -9873,31 +10053,39 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>172</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Order_resolved_dateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -9915,12 +10103,12 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>Order_resolved_dateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
@@ -9935,7 +10123,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>Closed time</t>
+          <t>Customer site id</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -9947,34 +10135,42 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>173</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>ldmnd_stat_id</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -9989,12 +10185,12 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>ldmnd_stat_id</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
@@ -10009,7 +10205,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>IMO status (codes)</t>
+          <t>Work order related</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -10021,31 +10217,39 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>174</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>material_status</t>
+          <t>recall_date</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10063,12 +10267,12 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>material_status</t>
+          <t>recall_date</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
@@ -10083,7 +10287,7 @@
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>IMO status (words)</t>
+          <t>Call management expected complete time</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
@@ -10095,31 +10299,39 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>recall_time</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10137,12 +10349,12 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>recall_time</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
@@ -10155,11 +10367,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O123" s="4" t="inlineStr">
-        <is>
-          <t>Part id initially requested for repair order</t>
-        </is>
-      </c>
+      <c r="O123" s="4" t="inlineStr"/>
       <c r="P123" s="4" t="inlineStr">
         <is>
           <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
@@ -10169,31 +10377,39 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>serial_no</t>
+          <t>resolve_date</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10211,12 +10427,12 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>serial_no</t>
+          <t>resolve_date</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
@@ -10229,11 +10445,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O124" s="4" t="inlineStr">
-        <is>
-          <t>Serial of item</t>
-        </is>
-      </c>
+      <c r="O124" s="4" t="inlineStr"/>
       <c r="P124" s="4" t="inlineStr">
         <is>
           <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
@@ -10243,31 +10455,39 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>to_warehouse_id</t>
+          <t>resolve_time</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10285,12 +10505,12 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>to_warehouse_id</t>
+          <t>resolve_time</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10303,11 +10523,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O125" s="4" t="inlineStr">
-        <is>
-          <t>NCR location responsible</t>
-        </is>
-      </c>
+      <c r="O125" s="4" t="inlineStr"/>
       <c r="P125" s="4" t="inlineStr">
         <is>
           <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
@@ -10317,34 +10533,42 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>from_warehouse_id</t>
+          <t>sla_eta_clock</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -10359,12 +10583,12 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>from_warehouse_id</t>
+          <t>sla_eta_clock</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -10379,7 +10603,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>NCR location where part originated</t>
+          <t>Time in seconds that was used to complete the ETA portion</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -10391,31 +10615,39 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Repair_Description</t>
+          <t>sla_eta_failure_code</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10433,12 +10665,12 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>Repair_Description</t>
+          <t>sla_eta_failure_code</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10451,11 +10683,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O127" s="4" t="inlineStr">
-        <is>
-          <t>Repair description (words)</t>
-        </is>
-      </c>
+      <c r="O127" s="4" t="inlineStr"/>
       <c r="P127" s="4" t="inlineStr">
         <is>
           <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
@@ -10465,31 +10693,39 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Repair_code</t>
+          <t>sla_eta_hit</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
-      <c r="G128" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10507,12 +10743,12 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>Repair_code</t>
+          <t>sla_eta_hit</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10525,11 +10761,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="O128" s="4" t="inlineStr">
-        <is>
-          <t>Repair description (codes)</t>
-        </is>
-      </c>
+      <c r="O128" s="4" t="inlineStr"/>
       <c r="P128" s="4" t="inlineStr">
         <is>
           <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
@@ -10539,34 +10771,42 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Work_order</t>
+          <t>sla_resolve_clock</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
+          <t>Not always available</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>Chase Sharepoint</t>
+        </is>
+      </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -10581,12 +10821,12 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>Work_order</t>
+          <t>sla_resolve_clock</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10601,7 +10841,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>Related work order order_id</t>
+          <t>Time in seconds that was used to complete the ticket</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -10613,22 +10853,22 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Updated_part_id</t>
+          <t>company_id</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Supplier info</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -10636,8 +10876,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>SAP Business Partners - cardcode</t>
+        </is>
+      </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10655,12 +10903,12 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>Updated_part_id</t>
+          <t>company_id</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10675,34 +10923,34 @@
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>Part actually used on repair job</t>
+          <t>Vendor id</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>RA_status</t>
+          <t>descr</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Supplier info</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -10710,8 +10958,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>SAP Business Partners - name</t>
+        </is>
+      </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
           <t>String</t>
@@ -10729,12 +10985,12 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>RA_status</t>
+          <t>descr</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10749,98 +11005,106 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>RA status</t>
+          <t>Vendor name</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>address_id</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>warehouse</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>warehouse details</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>is_vendor</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Supplier info</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>SAP Business Partners - customer/supplier flag</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
         <is>
           <t>SAP Service Layer</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Warehouses endpoint</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>address_id</t>
-        </is>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>Direct map after trimming text.</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>Site id</t>
-        </is>
-      </c>
-      <c r="P132" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed from MinStock3/Exco local sources; review business meaning where noted.</t>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>is_vendor</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>Do not populate until SAP source is proven.</t>
+        </is>
+      </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>Active supplier?</t>
+        </is>
+      </c>
+      <c r="P132" s="4" t="inlineStr">
+        <is>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>descr</t>
+          <t>address_id</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10858,11 +11122,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - if set up correctly every warehouse should have an address</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -10882,7 +11154,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>descr</t>
+          <t>address_id</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -10897,7 +11169,7 @@
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Site description</t>
+          <t>Site id</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
@@ -10909,12 +11181,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>is_repair_whse</t>
+          <t>descr</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10932,8 +11204,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -10956,7 +11236,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>is_repair_whse</t>
+          <t>descr</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -10971,7 +11251,7 @@
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>Internal repair location</t>
+          <t>Site description</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
@@ -11006,8 +11286,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - is active</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11057,12 +11345,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>node_id</t>
+          <t>return_warehouse</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -11080,11 +11368,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded back to MAIN?</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -11104,7 +11400,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>node_id</t>
+          <t>return_warehouse</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -11119,7 +11415,7 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Associated node</t>
+          <t>Preferred warehouse for return (faulty) stock for repair/scrap</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
@@ -11131,12 +11427,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>supply_warehouse</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -11154,8 +11450,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Hardcoded to MAIN?</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11178,7 +11482,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>person_id</t>
+          <t>supply_warehouse</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -11193,7 +11497,7 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Associated field engineer</t>
+          <t>Preferred warehouse for replenishment</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
@@ -11205,12 +11509,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>return_warehouse</t>
+          <t>warehouse_id</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11228,8 +11532,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - e.g. FUJITSU</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11252,7 +11564,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>return_warehouse</t>
+          <t>warehouse_id</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -11267,7 +11579,7 @@
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Preferred warehouse for return (faulty) stock for repair/scrap</t>
+          <t>Site id</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
@@ -11279,12 +11591,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>supply_warehouse</t>
+          <t>warehouse_type_id</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11302,8 +11614,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - e.g. Fujitsu South Africa Main Stock location - Johannesburg</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11326,7 +11646,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>supply_warehouse</t>
+          <t>warehouse_type_id</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11341,7 +11661,7 @@
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Preferred warehouse for replenishment</t>
+          <t>Site type - critical</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
@@ -11353,12 +11673,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>warehouse_id</t>
+          <t>cst_branch_stockable</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11376,11 +11696,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>All sites are branch stockable</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -11400,7 +11728,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>warehouse_id</t>
+          <t>cst_branch_stockable</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11415,7 +11743,7 @@
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Site id</t>
+          <t>Can this regional location accept stock</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
@@ -11427,12 +11755,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>warehouse_type_id</t>
+          <t>cst_active</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11450,11 +11778,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - is active</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -11474,7 +11810,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>warehouse_type_id</t>
+          <t>cst_active</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -11489,7 +11825,7 @@
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Site type - critical</t>
+          <t>Is site in current use?</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
@@ -11501,12 +11837,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>cst_boot_stockable</t>
+          <t>is_obsolete</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11524,11 +11860,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>SAP warehouse info - is active</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>String</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -11548,7 +11892,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>cst_boot_stockable</t>
+          <t>is_obsolete</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -11563,7 +11907,7 @@
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Can this technician accept stock</t>
+          <t>Is site in current use?</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
@@ -11575,12 +11919,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>cst_branch_stockable</t>
+          <t>lead_time</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11595,11 +11939,19 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
+          <t>Nice to have</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Hardcode</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Float</t>
@@ -11622,12 +11974,12 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>cst_branch_stockable</t>
+          <t>lead_time</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>Direct map after trimming text.</t>
+          <t>Parse to ISO datetime/date where source supports it.</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -11635,11 +11987,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="O143" s="2" t="inlineStr">
-        <is>
-          <t>Can this regional location accept stock</t>
-        </is>
-      </c>
+      <c r="O143" s="2" t="inlineStr"/>
       <c r="P143" s="2" t="inlineStr">
         <is>
           <t>Confirmed from MinStock3/Exco local sources; review business meaning where noted.</t>
@@ -11649,12 +11997,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>cst_active</t>
+          <t>cst_remote</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11672,11 +12020,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>String</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -11696,7 +12052,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>cst_active</t>
+          <t>cst_remote</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11711,7 +12067,7 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>Is site in current use?</t>
+          <t>Is site an outlying regional location</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
@@ -11723,22 +12079,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>is_obsolete</t>
+          <t>allocated_qty</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>whse_bpart_qty</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>warehouse details</t>
+          <t>Stock detail</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -11746,11 +12102,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -11765,17 +12129,17 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Warehouses endpoint</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>is_obsolete</t>
+          <t>allocated_qty</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>Direct map after trimming text.</t>
+          <t>Coerce to numeric quantity.</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11785,7 +12149,7 @@
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Is site in current use?</t>
+          <t>Committed stock to orders, not yet consumed</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
@@ -11797,22 +12161,22 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>cst_remote</t>
+          <t>part_id</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>whse_bpart_qty</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>warehouse details</t>
+          <t>Stock detail</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -11820,8 +12184,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11839,12 +12211,12 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Warehouses endpoint</t>
+          <t>SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>cst_remote</t>
+          <t>part_id</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -11859,7 +12231,7 @@
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>Is site an outlying regional location</t>
+          <t>Part number</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
@@ -11871,12 +12243,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>allocated_qty</t>
+          <t>in_bound_qty</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11894,8 +12266,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Float</t>
@@ -11918,7 +12298,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>allocated_qty</t>
+          <t>in_bound_qty</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -11933,7 +12313,7 @@
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Committed stock to orders, not yet consumed</t>
+          <t>Inbound to this site (in transit)</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
@@ -11945,12 +12325,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>inv_type_id</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11968,8 +12348,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>String</t>
@@ -11992,7 +12380,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>inv_type_id</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -12007,7 +12395,7 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Good or faulty inventory (faulty to be returned for repair or scrapping)</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
@@ -12019,12 +12407,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>in_bound_qty</t>
+          <t>out_bound_qty</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -12042,8 +12430,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Float</t>
@@ -12066,7 +12462,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>in_bound_qty</t>
+          <t>out_bound_qty</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -12081,7 +12477,7 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Inbound to this site (in transit)</t>
+          <t>Outbound stock from this site (in transit)</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
@@ -12093,12 +12489,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>inv_type_id</t>
+          <t>qty</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -12116,11 +12512,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -12140,12 +12544,12 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>inv_type_id</t>
+          <t>qty</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>Direct map after trimming text.</t>
+          <t>Coerce to numeric quantity.</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -12155,7 +12559,7 @@
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Good or faulty inventory (faulty to be returned for repair or scrapping)</t>
+          <t>Stock on hand</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
@@ -12167,12 +12571,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>out_bound_qty</t>
+          <t>warehouse_id</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12190,11 +12594,19 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>SAP Stock / warehouse detail</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>String</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -12214,12 +12626,12 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>out_bound_qty</t>
+          <t>warehouse_id</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>Coerce to numeric quantity.</t>
+          <t>Direct map after trimming text.</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -12229,7 +12641,7 @@
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Outbound stock from this site (in transit)</t>
+          <t>Warehouse location id</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
@@ -12238,156 +12650,8 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>whse_bpart_qty</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Stock detail</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Float</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>SQLQueries on OITW/OITM</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="inlineStr">
-        <is>
-          <t>Coerce to numeric quantity.</t>
-        </is>
-      </c>
-      <c r="N152" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>Stock on hand</t>
-        </is>
-      </c>
-      <c r="P152" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed from MinStock3/Exco local sources; review business meaning where noted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>warehouse_id</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>whse_bpart_qty</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Stock detail</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>SQLQueries on OITW/OITM</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>warehouse_id</t>
-        </is>
-      </c>
-      <c r="M153" s="2" t="inlineStr">
-        <is>
-          <t>Direct map after trimming text.</t>
-        </is>
-      </c>
-      <c r="N153" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="O153" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse location id</t>
-        </is>
-      </c>
-      <c r="P153" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed from MinStock3/Exco local sources; review business meaning where noted.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P153"/>
+  <autoFilter ref="A1:P151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -12971,36 +13235,40 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>SPLMaster</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Reference masters.csv:SPL Master by linked item</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15179,36 +15447,40 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>orderNumber</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:Document for DN rows</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15451,70 +15723,78 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>partCode</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr"/>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:Item No.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr"/>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:Whse</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15621,36 +15901,40 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>quantityUsed</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Float</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15689,36 +15973,40 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>partsUsedDateTime</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr"/>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:Posting Date</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18880,7 +19168,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Reference\SPL Planning Data Fields.xlsx</t>
+          <t>Reference\SPL Planning Data Fields edited.xlsx</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -18953,7 +19241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -22076,17 +22364,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>actual_eta_datetime</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -22096,7 +22384,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.order_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.actual_eta_datetime for CoCre8?</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -22113,17 +22401,17 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>repair_type</t>
+          <t>actual_recall_datetime</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -22133,7 +22421,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.repair_type for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.actual_recall_datetime for CoCre8?</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -22150,17 +22438,17 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>order_type_id</t>
+          <t>actual_resolve_date</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -22170,7 +22458,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.order_type_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.actual_resolve_date for CoCre8?</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -22187,17 +22475,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>creation_datetime</t>
+          <t>actual_resolve_time</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -22207,7 +22495,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.creation_datetime for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.actual_resolve_time for CoCre8?</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -22224,17 +22512,17 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Order_Open_dateTime</t>
+          <t>eta_date</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -22244,7 +22532,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Order_Open_dateTime for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.eta_date for CoCre8?</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -22261,17 +22549,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Item_received_dateTime</t>
+          <t>eta_time</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -22281,7 +22569,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Item_received_dateTime for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.eta_time for CoCre8?</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -22298,17 +22586,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Order_resolved_dateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -22318,7 +22606,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Order_resolved_dateTime for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.location for CoCre8?</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -22335,17 +22623,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>ldmnd_stat_id</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -22355,7 +22643,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.ldmnd_stat_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.order_id for CoCre8?</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -22372,17 +22660,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>material_status</t>
+          <t>recall_date</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -22392,7 +22680,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.material_status for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.recall_date for CoCre8?</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -22409,17 +22697,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>part_id</t>
+          <t>recall_time</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -22429,7 +22717,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.part_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.recall_time for CoCre8?</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -22446,17 +22734,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>serial_no</t>
+          <t>resolve_date</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -22466,7 +22754,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.serial_no for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.resolve_date for CoCre8?</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -22483,17 +22771,17 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>to_warehouse_id</t>
+          <t>resolve_time</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -22503,7 +22791,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.to_warehouse_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.resolve_time for CoCre8?</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -22520,17 +22808,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>from_warehouse_id</t>
+          <t>sla_eta_clock</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -22540,7 +22828,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.from_warehouse_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.sla_eta_clock for CoCre8?</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -22557,17 +22845,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Repair_Description</t>
+          <t>sla_eta_failure_code</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -22577,7 +22865,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Repair_Description for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.sla_eta_failure_code for CoCre8?</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -22594,17 +22882,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Repair_code</t>
+          <t>sla_eta_hit</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -22614,7 +22902,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Repair_code for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.sla_eta_hit for CoCre8?</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -22631,17 +22919,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Work_order</t>
+          <t>sla_resolve_clock</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Service call data - SLA compliance info per ticket</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -22651,7 +22939,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Work_order for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies service_call_env.sla_resolve_clock for CoCre8?</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -22668,17 +22956,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Updated_part_id</t>
+          <t>company_id</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Supplier info</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -22688,7 +22976,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.Updated_part_id for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies vendor.company_id for CoCre8?</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -22698,24 +22986,24 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>RA_status</t>
+          <t>descr</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>Supplier info</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -22725,7 +23013,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Which SAP Service Layer endpoint/table supplies repair_orders.RA_status for CoCre8?</t>
+          <t>Which SAP Service Layer endpoint/table supplies vendor.descr for CoCre8?</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -22735,24 +23023,24 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Important V2 vision object; not confirmed in current CC8 local sources.</t>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>is_vendor</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>vendor</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Planning V2 template</t>
+          <t>Supplier info</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -22762,24 +23050,24 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeId?</t>
+          <t>Which SAP Service Layer endpoint/table supplies vendor.is_vendor for CoCre8?</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+          <t>Run SAP metadata/query investigation and record result in SAP Investigation Log.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>V1 target field has no confirmed source.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>parentNodeId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -22799,7 +23087,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.parentNodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeId?</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -22816,7 +23104,7 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>nodeDescription</t>
+          <t>parentNodeId</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -22836,7 +23124,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Nodes.parentNodeId?</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -22853,12 +23141,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>nodeDescription</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Nodes</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -22868,12 +23156,12 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeDescription?</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -22883,14 +23171,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>customerGroupId</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -22910,7 +23198,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerId?</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -22920,14 +23208,14 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
+          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>customerGroupId</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -22947,7 +23235,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.Description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -22957,14 +23245,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -22984,7 +23272,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.Description?</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -22994,14 +23282,14 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
+          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -23021,7 +23309,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -23031,14 +23319,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
+          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>dseSlaCost</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -23058,7 +23346,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -23068,14 +23356,14 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
+          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>dseSlaRevenue</t>
+          <t>dseSlaCost</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -23095,7 +23383,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -23105,14 +23393,14 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
+          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>stdResponseTime</t>
+          <t>dseSlaRevenue</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -23132,7 +23420,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -23142,14 +23430,14 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard response time.</t>
+          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>stdRepairTime</t>
+          <t>stdResponseTime</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -23169,7 +23457,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -23179,19 +23467,19 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
+          <t>Left blank. User has no confirmed source yet for standard response time.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>stdRepairTime</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -23201,12 +23489,12 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -23216,14 +23504,14 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -23243,7 +23531,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.Description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorId?</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -23260,7 +23548,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -23280,7 +23568,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.Description?</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -23297,12 +23585,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>SPLMaster</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Vendors</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -23317,7 +23605,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.SPLMaster?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.isActive?</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -23327,7 +23615,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -25184,7 +25472,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -25204,7 +25492,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -25221,7 +25509,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -25241,7 +25529,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -25258,7 +25546,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -25278,7 +25566,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -25295,7 +25583,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -25315,7 +25603,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -25332,7 +25620,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -25352,7 +25640,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -25369,7 +25657,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -25389,7 +25677,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -25406,7 +25694,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -25426,7 +25714,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -25443,7 +25731,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -25463,7 +25751,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -25480,7 +25768,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -25500,7 +25788,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -25517,7 +25805,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -25537,7 +25825,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -25554,7 +25842,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -25574,7 +25862,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -25591,7 +25879,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -25611,7 +25899,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -25628,12 +25916,12 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -25648,7 +25936,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -25665,12 +25953,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -25685,7 +25973,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -25702,12 +25990,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -25722,7 +26010,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -25739,12 +26027,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -25759,7 +26047,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -25776,12 +26064,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -25796,7 +26084,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -25813,7 +26101,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -25833,7 +26121,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -25850,7 +26138,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -25870,7 +26158,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -25887,7 +26175,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -25907,7 +26195,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -25924,7 +26212,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -25944,7 +26232,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -25961,7 +26249,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -25981,7 +26269,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -25998,7 +26286,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -26018,7 +26306,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -26035,7 +26323,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -26055,7 +26343,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -26072,12 +26360,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -26092,7 +26380,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -26109,12 +26397,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -26129,7 +26417,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -26146,12 +26434,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -26166,7 +26454,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -26183,12 +26471,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -26203,7 +26491,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -26220,12 +26508,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -26240,7 +26528,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -26257,7 +26545,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -26277,7 +26565,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -26294,7 +26582,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -26314,7 +26602,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -26331,7 +26619,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -26351,7 +26639,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -26368,7 +26656,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -26388,7 +26676,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -26405,7 +26693,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -26425,7 +26713,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -26442,7 +26730,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -26462,7 +26750,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -26479,7 +26767,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -26499,7 +26787,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -26516,7 +26804,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -26536,7 +26824,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -26553,7 +26841,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -26573,7 +26861,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -26590,7 +26878,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -26610,7 +26898,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -26627,7 +26915,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -26647,7 +26935,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -26664,7 +26952,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -26684,7 +26972,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -26701,7 +26989,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -26721,7 +27009,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -26738,7 +27026,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -26758,7 +27046,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -26775,7 +27063,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -26795,7 +27083,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -26812,7 +27100,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -26832,7 +27120,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -26849,7 +27137,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -26869,7 +27157,7 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -26886,12 +27174,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -26906,7 +27194,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -26923,12 +27211,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -26943,7 +27231,7 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -26960,12 +27248,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -26980,7 +27268,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -26997,12 +27285,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -27017,7 +27305,7 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -27034,12 +27322,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>averageRepairCost</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -27054,7 +27342,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -27076,7 +27364,7 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -27091,7 +27379,7 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -27108,12 +27396,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -27128,7 +27416,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -27145,12 +27433,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -27165,7 +27453,7 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -27182,12 +27470,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -27202,7 +27490,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -27219,12 +27507,12 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>averageRepairCost</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
@@ -27239,7 +27527,7 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -27256,12 +27544,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -27276,7 +27564,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -27293,12 +27581,12 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -27313,7 +27601,7 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
@@ -27330,12 +27618,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -27350,7 +27638,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -27367,7 +27655,7 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -27387,7 +27675,7 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -27404,7 +27692,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -27424,7 +27712,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -27441,7 +27729,7 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>loClass</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -27461,7 +27749,7 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -27478,7 +27766,7 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -27498,7 +27786,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -27515,7 +27803,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -27535,7 +27823,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -27552,7 +27840,7 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -27572,7 +27860,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -27589,7 +27877,7 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -27609,7 +27897,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -27626,7 +27914,7 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>loClass</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -27646,7 +27934,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -27663,7 +27951,7 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -27683,7 +27971,7 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -27700,12 +27988,12 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>purchaseOrderNumber</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -27720,7 +28008,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -27737,12 +28025,12 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>purchaseOrderStatus</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -27757,7 +28045,7 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -27774,12 +28062,12 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>creationDateTime</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -27794,7 +28082,7 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -27811,12 +28099,12 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>approvalDateTime</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -27831,7 +28119,7 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -27848,12 +28136,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -27868,7 +28156,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -27885,7 +28173,7 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -27905,7 +28193,7 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -27922,7 +28210,7 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -27942,7 +28230,7 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -27959,7 +28247,7 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -27979,7 +28267,7 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -27996,7 +28284,7 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>approvalDateTime</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -28016,7 +28304,7 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -28033,7 +28321,7 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -28053,7 +28341,7 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -28070,7 +28358,7 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -28090,7 +28378,7 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -28107,7 +28395,7 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -28127,7 +28415,7 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -28144,7 +28432,7 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>lineCost</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -28164,7 +28452,7 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -28181,7 +28469,7 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>quantityReceived</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -28201,7 +28489,7 @@
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -28218,7 +28506,7 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>receivedDateTime</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -28238,7 +28526,7 @@
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -28255,12 +28543,12 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
@@ -28275,7 +28563,7 @@
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -28292,12 +28580,12 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -28312,7 +28600,7 @@
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -28329,12 +28617,12 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>lineCost</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -28349,7 +28637,7 @@
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -28366,12 +28654,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>quantityReceived</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -28386,7 +28674,7 @@
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -28403,12 +28691,12 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>receivedDateTime</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -28423,7 +28711,7 @@
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
@@ -28440,12 +28728,12 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode</t>
+          <t>actionGroupId</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -28460,7 +28748,7 @@
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -28477,12 +28765,12 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -28497,7 +28785,7 @@
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -28514,12 +28802,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>actionGroupDescription</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -28534,7 +28822,7 @@
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -28551,12 +28839,12 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -28571,7 +28859,7 @@
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -28588,12 +28876,12 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>isUsed</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>ActionGroups</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -28608,7 +28896,7 @@
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -28625,7 +28913,7 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>isObsolete</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -28645,7 +28933,7 @@
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -28662,12 +28950,12 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -28682,7 +28970,7 @@
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -28699,12 +28987,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>actionGroupDescription</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -28719,7 +29007,7 @@
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -28736,12 +29024,12 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>exclusion</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>ActionGroups</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -28756,7 +29044,7 @@
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -28770,193 +29058,8 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
-        <is>
-          <t>isUsed</t>
-        </is>
-      </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D266" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E266" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
-        </is>
-      </c>
-      <c r="F266" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G266" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>isObsolete</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D267" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E267" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
-        </is>
-      </c>
-      <c r="F267" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G267" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>warehouseId</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D268" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
-        </is>
-      </c>
-      <c r="F268" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G268" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D269" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E269" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="F269" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G269" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D270" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E270" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="F270" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G270" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G270"/>
+  <autoFilter ref="A1:G265"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -29457,7 +29560,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>SPLMaster; isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
+          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
         </is>
       </c>
     </row>
@@ -29570,29 +29673,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>PartsUsage.csv</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>orderNumber, requestId, customerCompanyCode, orderType, orderStatus, orderStartDatetime, requestTicketDateTime, siteCompanyCode, partCode, Warehouse, assignedPersonCode, resolvedDateTime, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, deviceSerialNumber</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>orderNumber; requestId; customerCompanyCode; orderType; orderStatus; orderStartDatetime; requestTicketDateTime; siteCompanyCode; partCode; Warehouse; assignedPersonCode; resolvedDateTime; serialNumber; quantityUsed; relCompanyId; partsUsedDateTime; deviceSerialNumber</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>requestId; customerCompanyCode; orderType; orderStatus; orderStartDatetime; requestTicketDateTime; siteCompanyCode; assignedPersonCode; resolvedDateTime; serialNumber; relCompanyId; deviceSerialNumber</t>
         </is>
       </c>
     </row>
@@ -29884,7 +29987,7 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="57" customWidth="1" min="2" max="2"/>
     <col width="61" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -30137,17 +30240,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>repair_orders</t>
+          <t>service_call_env</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ServiceCalls / inventory transfers / user tables</t>
+          <t>ServiceCalls / Activity endpoints / SQLQueries</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>repair order, return authorization, repair status and ETA</t>
+          <t>ETA, recall, resolve, SLA clocks and failure codes</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$249</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -94,6 +99,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G265" headerRowCount="1">
-  <autoFilter ref="A1:G265"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G249" headerRowCount="1">
+  <autoFilter ref="A1:G249"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -13705,70 +13713,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>isService</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>bpart.is_service is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>isTool</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>bpart.is_tool is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -13807,36 +13807,32 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>isSmallPart</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>bpart.cst_small_part is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -14405,40 +14401,36 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>nodeId</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>warehouse.node_id is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -14595,36 +14587,32 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>isRepairWarehouse</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>warehouse.is_repair_whse is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -14663,36 +14651,32 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>isBootStockable</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>warehouse.cst_boot_stockable is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -15163,40 +15147,36 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Employees</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>actionGroupId</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>person.actgr_id is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -15485,36 +15465,32 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>parts_usage.Request_ID is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -17337,36 +17313,32 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>averageRepairCost</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr"/>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>bpart_cost.avg_repair_cost is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -17711,36 +17683,32 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>loClass</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr"/>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D145" s="5" t="inlineStr"/>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr"/>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>imo.LO_Class is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -18629,206 +18597,182 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>actionGroupId</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr"/>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr"/>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D172" s="5" t="inlineStr"/>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr"/>
+      <c r="G172" s="5" t="inlineStr"/>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>actgr.actgr_id is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B173" s="5" t="inlineStr">
         <is>
           <t>nodeId</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C173" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr"/>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr"/>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D173" s="5" t="inlineStr"/>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr"/>
+      <c r="G173" s="5" t="inlineStr"/>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>actgr.node_id is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B174" s="5" t="inlineStr">
         <is>
           <t>actionGroupDescription</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="C174" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr"/>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D174" s="5" t="inlineStr"/>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr"/>
+      <c r="G174" s="5" t="inlineStr"/>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>actgr.descr is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B175" s="5" t="inlineStr">
         <is>
           <t>assignAnySkill</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C175" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr"/>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr"/>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D175" s="5" t="inlineStr"/>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr"/>
+      <c r="G175" s="5" t="inlineStr"/>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>Technician action groups are marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>isUsed</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr"/>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr"/>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D176" s="5" t="inlineStr"/>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr"/>
+      <c r="G176" s="5" t="inlineStr"/>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>actgr.is_used is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>isObsolete</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr"/>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D177" s="5" t="inlineStr"/>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr"/>
+      <c r="G177" s="5" t="inlineStr"/>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>actgr.is_obsolete is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -18985,242 +18929,242 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>MinStock3 SAP stock</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\MinStock3\extract_raw_stock.py</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>OITW/OITM SQL for item, warehouse, on hand, minimum, ordered.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>MinStock3 open PO</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\MinStock3\extract_raw_stock.py</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>OPOR/POR1 SQL for recent open purchase order quantity.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>MinStock3 SPL masters</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\MinStock3\map_masters.py</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>masters.csv maps linked items to SPLMaster/MasterKey.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>SAP live warehouse lookup</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Service Layer Warehouses endpoint</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>WarehouseCode and WarehouseName are fetched live for warehouses present in live stock rows.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>MinStock3 SPI</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\MinStock3\enrich_dimensions.py</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>SPI_DATA supplies return/repair/list/credit pricing and derived CoCre8 cost.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>MinStock3 usage</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\MinStock3\enrich_dimensions.py</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Stock audit DN rows aggregate annual usage.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Planning V2 live stock extract</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Service Layer SQLQueries on OITW/OITM</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Current stock metrics are fetched live from OITW: OnHand, IsCommited, OnOrder, MinStock, MaxStock, AvgPrice.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Manual stock audit report</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>C:\dev\cc8\Exco\source_data\Stock Audit Report.txt</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Allowed manual SAP report source for usage once mapped to the template.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Reference target fields</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Reference\SPL Planning Data Fields edited.xlsx</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Planning V2 target field metadata and CC8 relevance hints.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Planning V2 sample templates</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Samples\Templates raw.xlsx</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Canonical onboarding template fields used for template-shaped CSV outputs.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Live SAP item group check</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>MinStock3 SAP Service Layer credentials</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Checked Items and ItemGroups while VPN was connected. ItemGroups are broad customer/manufacturer groups such as FUJITSU, ACER, and CHOICE; sampled item master fields ItemType, ItemClass, and MaterialType are generic SAP classifications.</t>
         </is>
@@ -19241,7 +19185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -23918,7 +23862,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>isService</t>
+          <t>isExcludeFromReplenishment</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -23938,7 +23882,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isService?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -23955,7 +23899,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>isTool</t>
+          <t>purchaseLeadTimeDays</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -23975,7 +23919,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isTool?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -23992,7 +23936,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>isExcludeFromReplenishment</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -24012,7 +23956,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -24029,12 +23973,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>isSmallPart</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -24049,7 +23993,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isSmallPart?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -24059,19 +24003,19 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>purchaseLeadTimeDays</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -24086,7 +24030,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -24096,19 +24040,19 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>addressLine1</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -24123,7 +24067,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -24133,14 +24077,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -24160,7 +24104,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -24177,7 +24121,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -24197,7 +24141,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -24214,7 +24158,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>addressLine1</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -24234,7 +24178,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -24251,7 +24195,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -24271,7 +24215,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -24288,7 +24232,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -24308,7 +24252,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -24325,7 +24269,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -24345,7 +24289,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -24362,7 +24306,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -24382,7 +24326,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -24399,7 +24343,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -24419,7 +24363,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -24436,7 +24380,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -24456,7 +24400,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -24473,12 +24417,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -24488,12 +24432,12 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -24503,19 +24447,19 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>returnWarehouseId</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -24525,12 +24469,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -24540,19 +24484,19 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>supplyWarehouseId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Warehouses</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -24562,12 +24506,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -24577,14 +24521,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>warehouseTypeId</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -24604,7 +24548,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -24614,14 +24558,14 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
+          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>isReplenishable</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -24641,7 +24585,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -24651,14 +24595,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>Expected associated planning hierarchy node id. Data fields list this as warehouse.node_id / associated node.</t>
+          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>returnWarehouseId</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -24678,7 +24622,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -24688,14 +24632,14 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
+          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>supplyWarehouseId</t>
+          <t>isRemote</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -24715,7 +24659,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -24725,14 +24669,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
+          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>warehouseTypeId</t>
+          <t>warehouseStatusId</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -24752,7 +24696,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -24762,19 +24706,19 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
+          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>isRepairWarehouse</t>
+          <t>inventoryType</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -24784,12 +24728,12 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRepairWarehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -24799,19 +24743,19 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>Expected true when this is an internal repair location. Data dictionary field: is_repair_whse.</t>
+          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>isReplenishable</t>
+          <t>quantityOutbound</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -24821,12 +24765,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -24836,19 +24780,19 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
+          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>uniqueId</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -24863,7 +24807,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.uniqueId?</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -24873,19 +24817,19 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Expected true when technician/boot location can accept stock. Data fields: cst_boot_stockable.</t>
+          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -24895,12 +24839,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -24910,19 +24854,19 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>isRemote</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -24932,12 +24876,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -24947,19 +24891,19 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>warehouseStatusId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -24969,12 +24913,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -24984,19 +24928,19 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>inventoryType</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -25006,12 +24950,12 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -25021,19 +24965,19 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>quantityOutbound</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -25043,12 +24987,12 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -25058,19 +25002,19 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>uniqueId</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -25080,12 +25024,12 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.uniqueId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -25095,14 +25039,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -25122,7 +25066,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -25139,7 +25083,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -25159,7 +25103,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -25176,7 +25120,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -25196,7 +25140,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.actionGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -25213,12 +25157,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -25233,7 +25177,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -25250,12 +25194,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -25270,7 +25214,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -25287,12 +25231,12 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -25307,7 +25251,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -25324,12 +25268,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -25344,7 +25288,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -25361,12 +25305,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -25381,7 +25325,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -25398,12 +25342,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -25418,7 +25362,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -25435,12 +25379,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -25455,7 +25399,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -25472,7 +25416,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -25492,7 +25436,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -25509,7 +25453,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -25529,7 +25473,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -25546,7 +25490,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -25566,7 +25510,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -25583,7 +25527,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -25603,7 +25547,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -25620,12 +25564,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -25640,7 +25584,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -25657,12 +25601,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -25677,7 +25621,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -25694,12 +25638,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -25714,7 +25658,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -25731,12 +25675,12 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -25751,7 +25695,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -25768,12 +25712,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -25788,7 +25732,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -25805,12 +25749,12 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -25825,7 +25769,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -25842,12 +25786,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -25862,7 +25806,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -25879,12 +25823,12 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -25899,7 +25843,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -25916,7 +25860,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -25936,7 +25880,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -25953,7 +25897,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -25973,7 +25917,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -25990,7 +25934,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -26010,7 +25954,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -26027,7 +25971,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -26047,7 +25991,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -26064,12 +26008,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -26084,7 +26028,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -26101,12 +26045,12 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -26121,7 +26065,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -26138,12 +26082,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -26158,7 +26102,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -26175,12 +26119,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -26195,7 +26139,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -26212,12 +26156,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -26232,7 +26176,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -26249,12 +26193,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -26269,7 +26213,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -26286,12 +26230,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -26306,7 +26250,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -26323,12 +26267,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -26343,7 +26287,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -26360,7 +26304,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -26380,7 +26324,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -26397,7 +26341,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -26417,7 +26361,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -26434,7 +26378,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -26454,7 +26398,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -26471,7 +26415,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -26491,7 +26435,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -26508,7 +26452,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -26528,7 +26472,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -26545,7 +26489,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -26565,7 +26509,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -26582,7 +26526,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -26602,7 +26546,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -26619,7 +26563,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -26639,7 +26583,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -26656,7 +26600,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -26676,7 +26620,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -26693,7 +26637,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -26713,7 +26657,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -26730,7 +26674,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -26750,7 +26694,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -26767,7 +26711,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -26787,7 +26731,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -26804,7 +26748,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -26824,7 +26768,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -26841,7 +26785,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -26861,7 +26805,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -26878,12 +26822,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -26898,7 +26842,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -26915,12 +26859,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -26935,7 +26879,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -26952,12 +26896,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -26972,7 +26916,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -26989,12 +26933,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -27009,7 +26953,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -27026,12 +26970,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -27046,7 +26990,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -27063,12 +27007,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -27083,7 +27027,7 @@
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -27100,12 +27044,12 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -27120,7 +27064,7 @@
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -27137,12 +27081,12 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -27157,7 +27101,7 @@
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -27174,12 +27118,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -27194,7 +27138,7 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -27211,12 +27155,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -27231,7 +27175,7 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -27248,12 +27192,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -27268,7 +27212,7 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -27285,12 +27229,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -27305,7 +27249,7 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -27322,12 +27266,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>averageRepairCost</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -27342,7 +27286,7 @@
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageRepairCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -27359,12 +27303,12 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -27379,7 +27323,7 @@
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -27396,12 +27340,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -27416,7 +27360,7 @@
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -27433,12 +27377,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -27453,7 +27397,7 @@
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -27470,7 +27414,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -27490,7 +27434,7 @@
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -27507,7 +27451,7 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -27527,7 +27471,7 @@
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -27544,7 +27488,7 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -27564,7 +27508,7 @@
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -27581,7 +27525,7 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -27601,7 +27545,7 @@
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
@@ -27618,12 +27562,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>purchaseOrderNumber</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -27638,7 +27582,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -27655,12 +27599,12 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>purchaseOrderStatus</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -27675,7 +27619,7 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -27692,12 +27636,12 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>creationDateTime</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -27712,7 +27656,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -27729,12 +27673,12 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>loClass</t>
+          <t>approvalDateTime</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -27749,7 +27693,7 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.loClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -27766,12 +27710,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -27786,7 +27730,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -27803,12 +27747,12 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
@@ -27823,7 +27767,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -27840,12 +27784,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -27860,7 +27804,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -27877,12 +27821,12 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -27897,7 +27841,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -27914,12 +27858,12 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -27934,7 +27878,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -27951,12 +27895,12 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PurchaseOrders</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
@@ -27971,7 +27915,7 @@
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -27988,7 +27932,7 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -28008,7 +27952,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -28025,7 +27969,7 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -28045,7 +27989,7 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -28062,7 +28006,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>lineCost</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -28082,7 +28026,7 @@
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -28099,7 +28043,7 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>approvalDateTime</t>
+          <t>quantityReceived</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -28119,7 +28063,7 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -28136,7 +28080,7 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>receivedDateTime</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -28156,7 +28100,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -28173,12 +28117,12 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
@@ -28193,7 +28137,7 @@
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -28210,12 +28154,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -28230,7 +28174,7 @@
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -28247,12 +28191,12 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
@@ -28267,7 +28211,7 @@
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -28284,12 +28228,12 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -28304,7 +28248,7 @@
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -28321,12 +28265,12 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -28341,7 +28285,7 @@
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -28358,12 +28302,12 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -28378,7 +28322,7 @@
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -28395,12 +28339,12 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
@@ -28415,7 +28359,7 @@
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -28432,12 +28376,12 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>lineCost</t>
+          <t>exclusion</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -28452,7 +28396,7 @@
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -28466,600 +28410,8 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="4" t="inlineStr">
-        <is>
-          <t>quantityReceived</t>
-        </is>
-      </c>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C250" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D250" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
-        </is>
-      </c>
-      <c r="F250" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G250" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>receivedDateTime</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
-        </is>
-      </c>
-      <c r="F251" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G251" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="4" t="inlineStr">
-        <is>
-          <t>partTypeCode</t>
-        </is>
-      </c>
-      <c r="B252" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
-        </is>
-      </c>
-      <c r="F252" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G252" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E253" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
-        </is>
-      </c>
-      <c r="F253" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G253" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D254" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
-        </is>
-      </c>
-      <c r="F254" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G254" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D255" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="F255" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G255" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E256" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
-        </is>
-      </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G256" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>actionGroupId</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupId?</t>
-        </is>
-      </c>
-      <c r="F257" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G257" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="inlineStr">
-        <is>
-          <t>nodeId</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E258" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.nodeId?</t>
-        </is>
-      </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G258" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>actionGroupDescription</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.actionGroupDescription?</t>
-        </is>
-      </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G259" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>assignAnySkill</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D260" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E260" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.assignAnySkill?</t>
-        </is>
-      </c>
-      <c r="F260" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G260" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>isUsed</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D261" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E261" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isUsed?</t>
-        </is>
-      </c>
-      <c r="F261" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G261" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
-        <is>
-          <t>isObsolete</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E262" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ActionGroups.isObsolete?</t>
-        </is>
-      </c>
-      <c r="F262" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G262" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>warehouseId</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
-        </is>
-      </c>
-      <c r="F263" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G263" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D264" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E264" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="F264" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G264" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D265" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E265" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="F265" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G265" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G265"/>
+  <autoFilter ref="A1:G249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -29555,12 +28907,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>SPLMaster, PartNumber, isPrimary, primaryPartNumber, description, isBranchStockable, isBootStockable, productClass, productType, costCategory, partType, isKit, isObsolete, isService, isTool, isExcludeFromReplenishment, isSmallPart, purchaseLeadTimeDays, isCritical</t>
+          <t>SPLMaster, PartNumber, isPrimary, primaryPartNumber, description, isBranchStockable, isBootStockable, productClass, productType, costCategory, partType, isKit, isObsolete, isExcludeFromReplenishment, purchaseLeadTimeDays, isCritical</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isService; isTool; isExcludeFromReplenishment; isSmallPart; purchaseLeadTimeDays; isCritical</t>
+          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isExcludeFromReplenishment; purchaseLeadTimeDays; isCritical</t>
         </is>
       </c>
     </row>
@@ -29609,12 +28961,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>warehouseId, addressId, nodeId, returnWarehouseId, supplyWarehouseId, warehouseTypeId, warehouseDescription, isRepairWarehouse, isReplenishable, isBootStockable, isBranchStockable, isRemote, warehouseStatusId</t>
+          <t>warehouseId, addressId, returnWarehouseId, supplyWarehouseId, warehouseTypeId, warehouseDescription, isReplenishable, isBranchStockable, isRemote, warehouseStatusId</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>addressId; nodeId; returnWarehouseId; supplyWarehouseId; warehouseTypeId; isRepairWarehouse; isReplenishable; isBootStockable; isBranchStockable; isRemote; warehouseStatusId</t>
+          <t>addressId; returnWarehouseId; supplyWarehouseId; warehouseTypeId; isReplenishable; isBranchStockable; isRemote; warehouseStatusId</t>
         </is>
       </c>
     </row>
@@ -29663,12 +29015,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>personId, role, actionGroupId, addressId, nodeId, firstName, middleName, surname, isActive, telephoneNumber</t>
+          <t>personId, role, addressId, nodeId, firstName, middleName, surname, isActive, telephoneNumber</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>personId; role; actionGroupId; addressId; nodeId; firstName; middleName; surname; isActive; telephoneNumber</t>
+          <t>personId; role; addressId; nodeId; firstName; middleName; surname; isActive; telephoneNumber</t>
         </is>
       </c>
     </row>
@@ -29690,12 +29042,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>orderNumber, requestId, customerCompanyCode, orderType, orderStatus, orderStartDatetime, requestTicketDateTime, siteCompanyCode, partCode, Warehouse, assignedPersonCode, resolvedDateTime, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, deviceSerialNumber</t>
+          <t>orderNumber, customerCompanyCode, orderType, orderStatus, orderStartDatetime, requestTicketDateTime, siteCompanyCode, partCode, Warehouse, assignedPersonCode, resolvedDateTime, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, deviceSerialNumber</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>requestId; customerCompanyCode; orderType; orderStatus; orderStartDatetime; requestTicketDateTime; siteCompanyCode; assignedPersonCode; resolvedDateTime; serialNumber; relCompanyId; deviceSerialNumber</t>
+          <t>customerCompanyCode; orderType; orderStatus; orderStartDatetime; requestTicketDateTime; siteCompanyCode; assignedPersonCode; resolvedDateTime; serialNumber; relCompanyId; deviceSerialNumber</t>
         </is>
       </c>
     </row>
@@ -29771,12 +29123,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>partCode, cost, currencyCode, averageCost, averageRepairCost</t>
+          <t>partCode, cost, currencyCode, averageCost</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>partCode; cost; currencyCode; averageCost; averageRepairCost</t>
+          <t>partCode; cost; currencyCode; averageCost</t>
         </is>
       </c>
     </row>
@@ -29825,12 +29177,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId, createdDateTime, completedDateTime, fromWarehouseId, toWarehouseId, demandStatus, orderStatusIsClosed, loClass, movementType, addressId, isResolved, partNumber, quantity, shipListCode</t>
+          <t>inventoryTransferImoId, createdDateTime, completedDateTime, fromWarehouseId, toWarehouseId, demandStatus, orderStatusIsClosed, movementType, addressId, isResolved, partNumber, quantity, shipListCode</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId; createdDateTime; completedDateTime; fromWarehouseId; toWarehouseId; demandStatus; orderStatusIsClosed; loClass; movementType; addressId; isResolved; partNumber; quantity; shipListCode</t>
+          <t>inventoryTransferImoId; createdDateTime; completedDateTime; fromWarehouseId; toWarehouseId; demandStatus; orderStatusIsClosed; movementType; addressId; isResolved; partNumber; quantity; shipListCode</t>
         </is>
       </c>
     </row>
@@ -29916,31 +29268,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>ActionGroups</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>ActionGroups.csv</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>actionGroupId, nodeId, actionGroupDescription, assignAnySkill, isUsed, isObsolete</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>actionGroupId; nodeId; actionGroupDescription; assignAnySkill; isUsed; isObsolete</t>
-        </is>
-      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -30022,243 +29366,243 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>goods</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Items / ProductTrees</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>model-to-part/BOM relationship</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>ib_warehouse</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>EquipmentCards / SerialNumbers / BillOfMaterials</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>installed base, model, serial, site, BOM quantity</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>imo</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>InventoryTransferRequests / StockTransfers / SQLQueries</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>from/to warehouse, status, dates, quantities, linked order</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Items / ProductTrees</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>model ids and descriptions</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Warehouses / Branches / user tables</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>warehouse hierarchy and regional node</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>order_line</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>ServiceCalls / Orders / SQLQueries</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>work orders, customer/site, serial, open/resolve timestamps</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>person</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>EmployeesInfo / Contacts / SalesPersons</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>technician identity and active status</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>purchase_orders</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>PurchaseOrders / OPOR/POR1 / GoodsReceiptPO</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>PO line, vendor, quantity, GRN/receipt status</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>service_call_env</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ServiceCalls / Activity endpoints / SQLQueries</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>ETA, recall, resolve, SLA clocks and failure codes</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Blocked until query/endpoint is proven against CoCre8 SAP.</t>
         </is>

--- a/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Template_Field_Map.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$P$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$G$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
   </definedNames>
@@ -239,8 +239,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G249" headerRowCount="1">
-  <autoFilter ref="A1:G249"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:G235" headerRowCount="1">
+  <autoFilter ref="A1:G235"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -17917,206 +17917,230 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>purchaseOrderNumber</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr"/>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr"/>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.DocNum</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>purchaseOrderStatus</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr"/>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr"/>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.DocStatus/CANCELED mapped to template status</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>creationDateTime</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr"/>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.CreateDate</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>approvalDateTime</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr"/>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr"/>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.DocDate</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>toWarehouseId</t>
         </is>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D156" s="4" t="inlineStr"/>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.WhsCode</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>vendorId</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr"/>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.CardCode</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18155,274 +18179,282 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="inlineStr">
+      <c r="A159" s="5" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>customerId</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr"/>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D159" s="5" t="inlineStr"/>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr"/>
+      <c r="G159" s="5" t="inlineStr"/>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>requestTicketDateTime</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C160" s="5" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr"/>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D160" s="5" t="inlineStr"/>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr"/>
+      <c r="G160" s="5" t="inlineStr"/>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B161" s="5" t="inlineStr">
         <is>
           <t>isResolved</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C161" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr"/>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr"/>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D161" s="5" t="inlineStr"/>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr"/>
+      <c r="G161" s="5" t="inlineStr"/>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>partNumber</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr"/>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.ItemCode</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.Quantity</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>lineCost</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr"/>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.LineTotal</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>quantityReceived</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:PDN1.Quantity summed by PO line</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>receivedDateTime</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr"/>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPDN.DocDate max by PO line</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -27562,7 +27594,7 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -27582,7 +27614,7 @@
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -27599,12 +27631,12 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -27619,7 +27651,7 @@
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.purchaseOrderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -27636,12 +27668,12 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -27656,7 +27688,7 @@
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.creationDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -27673,12 +27705,12 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>approvalDateTime</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -27693,7 +27725,7 @@
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.approvalDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -27710,12 +27742,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -27730,7 +27762,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -27747,12 +27779,12 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
@@ -27767,7 +27799,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -27784,12 +27816,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -27804,7 +27836,7 @@
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -27821,12 +27853,12 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -27841,7 +27873,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -27858,12 +27890,12 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>exclusion</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>PurchaseOrders</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -27878,7 +27910,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -27892,526 +27924,8 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>isResolved</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.isResolved?</t>
-        </is>
-      </c>
-      <c r="F236" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G236" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D237" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.partNumber?</t>
-        </is>
-      </c>
-      <c r="F237" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G237" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B238" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C238" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D238" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E238" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantity?</t>
-        </is>
-      </c>
-      <c r="F238" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G238" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>lineCost</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D239" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.lineCost?</t>
-        </is>
-      </c>
-      <c r="F239" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G239" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>quantityReceived</t>
-        </is>
-      </c>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C240" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D240" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.quantityReceived?</t>
-        </is>
-      </c>
-      <c r="F240" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G240" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>receivedDateTime</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C241" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D241" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E241" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.receivedDateTime?</t>
-        </is>
-      </c>
-      <c r="F241" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G241" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>partTypeCode</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
-        </is>
-      </c>
-      <c r="F242" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G242" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C243" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D243" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
-        </is>
-      </c>
-      <c r="F243" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G243" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
-        </is>
-      </c>
-      <c r="F244" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G244" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G245" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
-        </is>
-      </c>
-      <c r="F246" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G246" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>warehouseId</t>
-        </is>
-      </c>
-      <c r="B247" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C247" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D247" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E247" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
-        </is>
-      </c>
-      <c r="F247" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G247" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C248" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E248" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="F248" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G248" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="F249" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="G249" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G249"/>
+  <autoFilter ref="A1:G235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -29187,29 +28701,29 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders.csv</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>purchaseOrderNumber, purchaseOrderStatus, creationDateTime, approvalDateTime, toWarehouseId, vendorId, demandStatus, customerId, requestTicketDateTime, isResolved, partNumber, quantity, lineCost, quantityReceived, receivedDateTime</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>purchaseOrderNumber; purchaseOrderStatus; creationDateTime; approvalDateTime; toWarehouseId; vendorId; demandStatus; customerId; requestTicketDateTime; isResolved; partNumber; quantity; lineCost; quantityReceived; receivedDateTime</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>purchaseOrderNumber, purchaseOrderStatus, creationDateTime, approvalDateTime, toWarehouseId, vendorId, demandStatus, partNumber, quantity, lineCost, quantityReceived, receivedDateTime</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
         </is>
       </c>
     </row>
